--- a/Financial Analysis/LDO.xlsx
+++ b/Financial Analysis/LDO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B96168-D5CA-4F4F-87B1-DE88D9700F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C71A92D-D05D-4DC6-85BE-CD5B5D93B7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{22A8C101-2C37-4C84-8F61-6F009BD8F000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>LDO</t>
   </si>
@@ -206,16 +206,26 @@
   </si>
   <si>
     <t>Net operating expense</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +256,15 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -294,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -313,6 +332,8 @@
     <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,14 +731,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="8">
-        <v>47.27</v>
+        <v>55.8</v>
       </c>
       <c r="E3" s="11">
-        <v>45904</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45904</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="11">
         <v>45868</v>
@@ -741,7 +762,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>27246.428</v>
+        <v>32163.119999999995</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -783,7 +804,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>27513.428</v>
+        <v>32430.119999999995</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821B3318-0973-4389-8D9D-A6FE019E4DEA}">
-  <dimension ref="B2:EL32"/>
+  <dimension ref="B2:EL34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1300,7 +1321,7 @@
         <v>961.39985760000013</v>
       </c>
       <c r="AD7" s="5">
-        <f t="shared" ref="AD7:AJ7" si="11">AC7*1.02</f>
+        <f t="shared" ref="AD7:AE7" si="11">AC7*1.02</f>
         <v>980.62785475200019</v>
       </c>
       <c r="AE7" s="5">
@@ -1366,7 +1387,7 @@
         <v>112.57020000000011</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" ref="AA8:AJ8" si="14">AA8*1.05</f>
+        <f t="shared" ref="AB8:AJ8" si="14">AA8*1.05</f>
         <v>118.19871000000012</v>
       </c>
       <c r="AC8" s="5">
@@ -1563,71 +1584,71 @@
         <v>243</v>
       </c>
       <c r="T11" s="4">
-        <f>T5-T10</f>
+        <f t="shared" ref="T11:AJ11" si="18">T5-T10</f>
         <v>993</v>
       </c>
       <c r="U11" s="4">
-        <f>U5-U10</f>
+        <f t="shared" si="18"/>
         <v>494</v>
       </c>
       <c r="V11" s="4">
-        <f>V5-V10</f>
+        <f t="shared" si="18"/>
         <v>787</v>
       </c>
       <c r="W11" s="4">
-        <f>W5-W10</f>
+        <f t="shared" si="18"/>
         <v>829</v>
       </c>
       <c r="X11" s="4">
-        <f>X5-X10</f>
+        <f t="shared" si="18"/>
         <v>931</v>
       </c>
       <c r="Y11" s="4">
-        <f>Y5-Y10</f>
+        <f t="shared" si="18"/>
         <v>1180</v>
       </c>
       <c r="Z11" s="4">
-        <f>Z5-Z10</f>
+        <f t="shared" si="18"/>
         <v>1279.7501999999999</v>
       </c>
       <c r="AA11" s="4">
-        <f>AA5-AA10</f>
+        <f t="shared" si="18"/>
         <v>2337.6580199999999</v>
       </c>
       <c r="AB11" s="4">
-        <f>AB5-AB10</f>
+        <f t="shared" si="18"/>
         <v>2479.0432031999999</v>
       </c>
       <c r="AC11" s="4">
-        <f>AC5-AC10</f>
+        <f t="shared" si="18"/>
         <v>2577.0229442280001</v>
       </c>
       <c r="AD11" s="4">
-        <f>AD5-AD10</f>
+        <f t="shared" si="18"/>
         <v>2651.8514596448404</v>
       </c>
       <c r="AE11" s="4">
-        <f>AE5-AE10</f>
+        <f t="shared" si="18"/>
         <v>2700.979066504487</v>
       </c>
       <c r="AF11" s="4">
-        <f>AF5-AF10</f>
+        <f t="shared" si="18"/>
         <v>2750.8937543846641</v>
       </c>
       <c r="AG11" s="4">
-        <f>AG5-AG10</f>
+        <f t="shared" si="18"/>
         <v>2801.6014913499494</v>
       </c>
       <c r="AH11" s="4">
-        <f>AH5-AH10</f>
+        <f t="shared" si="18"/>
         <v>2853.1078761484196</v>
       </c>
       <c r="AI11" s="4">
-        <f>AI5-AI10</f>
+        <f t="shared" si="18"/>
         <v>2905.4181063914334</v>
       </c>
       <c r="AJ11" s="4">
-        <f>AJ5-AJ10</f>
+        <f t="shared" si="18"/>
         <v>2958.536944875309</v>
       </c>
     </row>
@@ -1662,39 +1683,39 @@
         <v>-357</v>
       </c>
       <c r="AB12" s="5">
-        <f t="shared" ref="AB12:AJ12" si="18">AA12*1.02</f>
+        <f t="shared" ref="AB12:AJ12" si="19">AA12*1.02</f>
         <v>-364.14</v>
       </c>
       <c r="AC12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-371.4228</v>
       </c>
       <c r="AD12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-378.85125599999998</v>
       </c>
       <c r="AE12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-386.42828112000001</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-394.15684674240003</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-402.03998367724802</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-410.08078335079301</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-418.28239901780887</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-426.64804699816506</v>
       </c>
     </row>
@@ -1726,43 +1747,43 @@
         <v>396.78000000000003</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" ref="AA13:AJ13" si="19">Z13*1.02</f>
+        <f t="shared" ref="AA13:AJ13" si="20">Z13*1.02</f>
         <v>404.71560000000005</v>
       </c>
       <c r="AB13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>412.80991200000005</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>421.06611024000006</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>429.48743244480005</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>438.07718109369608</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>446.83872471557004</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>455.77549920988145</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>464.89100919407906</v>
       </c>
       <c r="AI13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>474.18882937796064</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>483.67260596551989</v>
       </c>
     </row>
@@ -1794,43 +1815,43 @@
         <v>-123.42</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" ref="AA14:AJ14" si="20">Z14*1.02</f>
+        <f t="shared" ref="AA14:AJ14" si="21">Z14*1.02</f>
         <v>-125.8884</v>
       </c>
       <c r="AB14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-128.40616800000001</v>
       </c>
       <c r="AC14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-130.97429136000002</v>
       </c>
       <c r="AD14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-133.59377718720003</v>
       </c>
       <c r="AE14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-136.26565273094403</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-138.99096578556291</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-141.77078510127416</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-144.60620080329963</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-147.49832481936562</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-150.44829131575293</v>
       </c>
     </row>
@@ -1840,71 +1861,71 @@
       </c>
       <c r="P15" s="5"/>
       <c r="T15" s="5">
-        <f t="shared" ref="T15:Y15" si="21">SUM(T12:T14)</f>
+        <f t="shared" ref="T15:Y15" si="22">SUM(T12:T14)</f>
         <v>124</v>
       </c>
       <c r="U15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>241</v>
       </c>
       <c r="V15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>34</v>
       </c>
       <c r="W15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-154</v>
       </c>
       <c r="X15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>107</v>
       </c>
       <c r="Y15" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-266</v>
       </c>
       <c r="Z15" s="5">
-        <f t="shared" ref="Z15:AJ15" si="22">SUM(Z12:Z14)</f>
+        <f t="shared" ref="Z15:AJ15" si="23">SUM(Z12:Z14)</f>
         <v>-76.639999999999972</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-78.172799999999953</v>
       </c>
       <c r="AB15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-79.736255999999941</v>
       </c>
       <c r="AC15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-81.330981119999961</v>
       </c>
       <c r="AD15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-82.957600742399961</v>
       </c>
       <c r="AE15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-84.616752757247951</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-86.309087812392903</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-88.035269568640729</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-89.795974960013581</v>
       </c>
       <c r="AI15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-91.591894459213847</v>
       </c>
       <c r="AJ15" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-93.42373234839809</v>
       </c>
     </row>
@@ -1914,71 +1935,71 @@
       </c>
       <c r="P16" s="4"/>
       <c r="T16" s="4">
-        <f t="shared" ref="T16:Y16" si="23">T11-T15</f>
+        <f t="shared" ref="T16:Y16" si="24">T11-T15</f>
         <v>869</v>
       </c>
       <c r="U16" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>253</v>
       </c>
       <c r="V16" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>753</v>
       </c>
       <c r="W16" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>983</v>
       </c>
       <c r="X16" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>824</v>
       </c>
       <c r="Y16" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1446</v>
       </c>
       <c r="Z16" s="4">
-        <f t="shared" ref="Z16:AJ16" si="24">Z11-Z15</f>
+        <f t="shared" ref="Z16:AJ16" si="25">Z11-Z15</f>
         <v>1356.3901999999998</v>
       </c>
       <c r="AA16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2415.8308199999997</v>
       </c>
       <c r="AB16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2558.7794592</v>
       </c>
       <c r="AC16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2658.3539253480003</v>
       </c>
       <c r="AD16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2734.8090603872402</v>
       </c>
       <c r="AE16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2785.595819261735</v>
       </c>
       <c r="AF16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2837.2028421970572</v>
       </c>
       <c r="AG16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2889.63676091859</v>
       </c>
       <c r="AH16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2942.9038511084332</v>
       </c>
       <c r="AI16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2997.0100008506474</v>
       </c>
       <c r="AJ16" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3051.9606772237071</v>
       </c>
     </row>
@@ -2010,43 +2031,43 @@
         <v>244.15023599999995</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" ref="AA17:AJ17" si="25">AA16*0.18</f>
+        <f t="shared" ref="AA17:AJ17" si="26">AA16*0.18</f>
         <v>434.84954759999994</v>
       </c>
       <c r="AB17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>460.58030265599996</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>478.50370656264005</v>
       </c>
       <c r="AD17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>492.26563086970322</v>
       </c>
       <c r="AE17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>501.40724746711226</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>510.69651159547027</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>520.13461696534614</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>529.72269319951795</v>
       </c>
       <c r="AI17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>539.46180015311654</v>
       </c>
       <c r="AJ17" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>549.35292190026723</v>
       </c>
     </row>
@@ -2078,43 +2099,43 @@
         <v>94.947313999999992</v>
       </c>
       <c r="AA18" s="5">
-        <f t="shared" ref="AA18:AJ18" si="26">AA16*0.07</f>
+        <f t="shared" ref="AA18:AJ18" si="27">AA16*0.07</f>
         <v>169.10815739999998</v>
       </c>
       <c r="AB18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>179.11456214400002</v>
       </c>
       <c r="AC18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>186.08477477436003</v>
       </c>
       <c r="AD18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>191.43663422710682</v>
       </c>
       <c r="AE18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>194.99170734832146</v>
       </c>
       <c r="AF18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>198.60419895379403</v>
       </c>
       <c r="AG18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>202.27457326430132</v>
       </c>
       <c r="AH18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>206.00326957759034</v>
       </c>
       <c r="AI18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>209.79070005954534</v>
       </c>
       <c r="AJ18" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>213.63724740565951</v>
       </c>
     </row>
@@ -2147,71 +2168,71 @@
         <v>124</v>
       </c>
       <c r="T19" s="4">
-        <f t="shared" ref="T19:Y19" si="27">T16-T17-T18</f>
+        <f t="shared" ref="T19:Y19" si="28">T16-T17-T18</f>
         <v>823</v>
       </c>
       <c r="U19" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>239</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>586</v>
       </c>
       <c r="W19" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>927</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>658</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1072</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" ref="Z19:AJ19" si="28">Z16-Z17-Z18</f>
+        <f t="shared" ref="Z19:AJ19" si="29">Z16-Z17-Z18</f>
         <v>1017.2926499999999</v>
       </c>
       <c r="AA19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1811.8731149999999</v>
       </c>
       <c r="AB19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1919.0845944000002</v>
       </c>
       <c r="AC19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1993.765444011</v>
       </c>
       <c r="AD19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2051.10679529043</v>
       </c>
       <c r="AE19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2089.1968644463009</v>
       </c>
       <c r="AF19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2127.9021316477929</v>
       </c>
       <c r="AG19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2167.2275706889427</v>
       </c>
       <c r="AH19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2207.177888331325</v>
       </c>
       <c r="AI19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2247.7575006379852</v>
       </c>
       <c r="AJ19" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2288.9705079177807</v>
       </c>
       <c r="AK19" s="3">
@@ -2219,423 +2240,423 @@
         <v>2266.0808028386027</v>
       </c>
       <c r="AL19" s="3">
-        <f t="shared" ref="AL19:CW19" si="29">AK19*(1+$AM$24)</f>
+        <f t="shared" ref="AL19:CW19" si="30">AK19*(1+$AM$24)</f>
         <v>2243.4199948102168</v>
       </c>
       <c r="AM19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2220.9857948621147</v>
       </c>
       <c r="AN19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2198.7759369134938</v>
       </c>
       <c r="AO19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2176.7881775443589</v>
       </c>
       <c r="AP19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2155.0202957689153</v>
       </c>
       <c r="AQ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2133.4700928112261</v>
       </c>
       <c r="AR19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2112.1353918831137</v>
       </c>
       <c r="AS19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2091.0140379642826</v>
       </c>
       <c r="AT19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2070.1038975846395</v>
       </c>
       <c r="AU19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2049.4028586087929</v>
       </c>
       <c r="AV19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2028.9088300227049</v>
       </c>
       <c r="AW19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2008.6197417224778</v>
       </c>
       <c r="AX19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1988.5335443052529</v>
       </c>
       <c r="AY19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1968.6482088622004</v>
       </c>
       <c r="AZ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1948.9617267735784</v>
       </c>
       <c r="BA19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1929.4721095058426</v>
       </c>
       <c r="BB19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1910.177388410784</v>
       </c>
       <c r="BC19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1891.0756145266762</v>
       </c>
       <c r="BD19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1872.1648583814094</v>
       </c>
       <c r="BE19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1853.4432097975953</v>
       </c>
       <c r="BF19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1834.9087776996193</v>
       </c>
       <c r="BG19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1816.5596899226232</v>
       </c>
       <c r="BH19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1798.3940930233969</v>
       </c>
       <c r="BI19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1780.4101520931629</v>
       </c>
       <c r="BJ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1762.6060505722312</v>
       </c>
       <c r="BK19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1744.9799900665089</v>
       </c>
       <c r="BL19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1727.5301901658438</v>
       </c>
       <c r="BM19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1710.2548882641854</v>
       </c>
       <c r="BN19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1693.1523393815435</v>
       </c>
       <c r="BO19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1676.220815987728</v>
       </c>
       <c r="BP19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1659.4586078278508</v>
       </c>
       <c r="BQ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1642.8640217495722</v>
       </c>
       <c r="BR19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1626.4353815320765</v>
       </c>
       <c r="BS19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1610.1710277167556</v>
       </c>
       <c r="BT19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1594.0693174395881</v>
       </c>
       <c r="BU19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1578.1286242651922</v>
       </c>
       <c r="BV19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1562.3473380225403</v>
       </c>
       <c r="BW19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1546.7238646423148</v>
       </c>
       <c r="BX19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1531.2566259958917</v>
       </c>
       <c r="BY19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1515.9440597359328</v>
       </c>
       <c r="BZ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1500.7846191385734</v>
       </c>
       <c r="CA19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1485.7767729471875</v>
       </c>
       <c r="CB19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1470.9190052177157</v>
       </c>
       <c r="CC19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1456.2098151655387</v>
       </c>
       <c r="CD19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1441.6477170138833</v>
       </c>
       <c r="CE19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1427.2312398437443</v>
       </c>
       <c r="CF19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1412.9589274453069</v>
       </c>
       <c r="CG19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1398.8293381708538</v>
       </c>
       <c r="CH19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1384.8410447891454</v>
       </c>
       <c r="CI19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1370.992634341254</v>
       </c>
       <c r="CJ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1357.2827079978415</v>
       </c>
       <c r="CK19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1343.7098809178631</v>
       </c>
       <c r="CL19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1330.2727821086844</v>
       </c>
       <c r="CM19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1316.9700542875976</v>
       </c>
       <c r="CN19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1303.8003537447216</v>
       </c>
       <c r="CO19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1290.7623502072745</v>
       </c>
       <c r="CP19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1277.8547267052018</v>
       </c>
       <c r="CQ19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1265.0761794381497</v>
       </c>
       <c r="CR19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1252.4254176437682</v>
       </c>
       <c r="CS19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1239.9011634673307</v>
       </c>
       <c r="CT19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1227.5021518326573</v>
       </c>
       <c r="CU19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1215.2271303143307</v>
       </c>
       <c r="CV19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1203.0748590111873</v>
       </c>
       <c r="CW19" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1191.0441104210754</v>
       </c>
       <c r="CX19" s="3">
-        <f t="shared" ref="CX19:EL19" si="30">CW19*(1+$AM$24)</f>
+        <f t="shared" ref="CX19:EL19" si="31">CW19*(1+$AM$24)</f>
         <v>1179.1336693168646</v>
       </c>
       <c r="CY19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1167.3423326236959</v>
       </c>
       <c r="CZ19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1155.6689092974589</v>
       </c>
       <c r="DA19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1144.1122202044842</v>
       </c>
       <c r="DB19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1132.6710980024393</v>
       </c>
       <c r="DC19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1121.3443870224148</v>
       </c>
       <c r="DD19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1110.1309431521906</v>
       </c>
       <c r="DE19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1099.0296337206687</v>
       </c>
       <c r="DF19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1088.039337383462</v>
       </c>
       <c r="DG19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1077.1589440096275</v>
       </c>
       <c r="DH19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1066.3873545695312</v>
       </c>
       <c r="DI19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1055.7234810238358</v>
       </c>
       <c r="DJ19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1045.1662462135973</v>
       </c>
       <c r="DK19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1034.7145837514613</v>
       </c>
       <c r="DL19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1024.3674379139468</v>
       </c>
       <c r="DM19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1014.1237635348073</v>
       </c>
       <c r="DN19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1003.9825258994592</v>
       </c>
       <c r="DO19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>993.94270064046464</v>
       </c>
       <c r="DP19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>984.00327363405995</v>
       </c>
       <c r="DQ19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>974.16324089771933</v>
       </c>
       <c r="DR19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>964.42160848874209</v>
       </c>
       <c r="DS19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>954.77739240385472</v>
       </c>
       <c r="DT19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>945.22961847981617</v>
       </c>
       <c r="DU19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>935.77732229501805</v>
       </c>
       <c r="DV19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>926.41954907206787</v>
       </c>
       <c r="DW19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>917.15535358134719</v>
       </c>
       <c r="DX19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>907.98380004553371</v>
       </c>
       <c r="DY19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>898.9039620450784</v>
       </c>
       <c r="DZ19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>889.91492242462766</v>
       </c>
       <c r="EA19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>881.01577320038143</v>
       </c>
       <c r="EB19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>872.20561546837757</v>
       </c>
       <c r="EC19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>863.48355931369383</v>
       </c>
       <c r="ED19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>854.8487237205569</v>
       </c>
       <c r="EE19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>846.30023648335134</v>
       </c>
       <c r="EF19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>837.83723411851781</v>
       </c>
       <c r="EG19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>829.45886177733257</v>
       </c>
       <c r="EH19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>821.16427315955923</v>
       </c>
       <c r="EI19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>812.95263042796364</v>
       </c>
       <c r="EJ19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>804.82310412368395</v>
       </c>
       <c r="EK19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>796.77487308244713</v>
       </c>
       <c r="EL19" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>788.80712435162263</v>
       </c>
     </row>
@@ -2663,47 +2684,47 @@
         <v>575.6</v>
       </c>
       <c r="Z20" s="5">
-        <f>576.4</f>
+        <f t="shared" ref="Z20:AJ20" si="32">576.4</f>
         <v>576.4</v>
       </c>
       <c r="AA20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AB20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AC20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AD20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AE20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AF20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AG20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AH20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AI20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
       <c r="AJ20" s="5">
-        <f>576.4</f>
+        <f t="shared" si="32"/>
         <v>576.4</v>
       </c>
     </row>
@@ -2713,71 +2734,71 @@
       </c>
       <c r="P21" s="6"/>
       <c r="T21" s="6">
-        <f t="shared" ref="T21:Y21" si="31">T19/T20</f>
+        <f t="shared" ref="T21:Y21" si="33">T19/T20</f>
         <v>1.4298123697011813</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.41521890201528838</v>
       </c>
       <c r="V21" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.0180681028492007</v>
       </c>
       <c r="W21" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.6104933981931897</v>
       </c>
       <c r="X21" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.1431549687282836</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.862404447533009</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" ref="Z21:AJ21" si="32">Z19/Z20</f>
+        <f t="shared" ref="Z21:AJ21" si="34">Z19/Z20</f>
         <v>1.7649074427480915</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.1434301092990977</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.3294319819569749</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.458996259561069</v>
       </c>
       <c r="AD21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.5584781320097676</v>
       </c>
       <c r="AE21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.6245608335293218</v>
       </c>
       <c r="AF21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.6917108460232355</v>
       </c>
       <c r="AG21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.7599367985581935</v>
       </c>
       <c r="AH21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.8292468569245752</v>
       </c>
       <c r="AI21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.8996486825780452</v>
       </c>
       <c r="AJ21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.9711493891703342</v>
       </c>
     </row>
@@ -2804,67 +2825,67 @@
         <v>0.10159685258042117</v>
       </c>
       <c r="U23" s="7">
-        <f>U3/T3-1</f>
+        <f t="shared" ref="U23:AJ23" si="35">U3/T3-1</f>
         <v>-2.7132907719094601E-2</v>
       </c>
       <c r="V23" s="7">
-        <f>V3/U3-1</f>
+        <f t="shared" si="35"/>
         <v>5.4064131245339375E-2</v>
       </c>
       <c r="W23" s="7">
-        <f>W3/V3-1</f>
+        <f t="shared" si="35"/>
         <v>4.0891404315528845E-2</v>
       </c>
       <c r="X23" s="7">
-        <f>X3/W3-1</f>
+        <f t="shared" si="35"/>
         <v>3.9284986066743688E-2</v>
       </c>
       <c r="Y23" s="7">
-        <f>Y3/X3-1</f>
+        <f t="shared" si="35"/>
         <v>0.1616637237590739</v>
       </c>
       <c r="Z23" s="7">
-        <f>Z3/Y3-1</f>
+        <f t="shared" si="35"/>
         <v>0.1399999999999999</v>
       </c>
       <c r="AA23" s="7">
-        <f>AA3/Z3-1</f>
+        <f t="shared" si="35"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AB23" s="7">
-        <f>AB3/AA3-1</f>
+        <f t="shared" si="35"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AC23" s="7">
-        <f>AC3/AB3-1</f>
+        <f t="shared" si="35"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AD23" s="7">
-        <f>AD3/AC3-1</f>
+        <f t="shared" si="35"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE23" s="7">
-        <f>AE3/AD3-1</f>
+        <f t="shared" si="35"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF23" s="7">
-        <f>AF3/AE3-1</f>
+        <f t="shared" si="35"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG23" s="7">
-        <f>AG3/AF3-1</f>
+        <f t="shared" si="35"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH23" s="7">
-        <f>AH3/AG3-1</f>
+        <f t="shared" si="35"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI23" s="7">
-        <f>AI3/AH3-1</f>
+        <f t="shared" si="35"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ23" s="7">
-        <f>AJ3/AI3-1</f>
+        <f t="shared" si="35"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -2873,103 +2894,103 @@
         <v>45</v>
       </c>
       <c r="I24" s="7">
-        <f>I5/I3</f>
+        <f t="shared" ref="I24:P24" si="36">I5/I3</f>
         <v>0.1045925925925926</v>
       </c>
       <c r="J24" s="7">
-        <f>J5/J3</f>
+        <f t="shared" si="36"/>
         <v>0.1419753086419753</v>
       </c>
       <c r="K24" s="7">
-        <f>K5/K3</f>
+        <f t="shared" si="36"/>
         <v>9.4159388646288214E-2</v>
       </c>
       <c r="L24" s="7">
-        <f>L5/L3</f>
+        <f t="shared" si="36"/>
         <v>0.10344827586206896</v>
       </c>
       <c r="M24" s="7">
-        <f>M5/M3</f>
+        <f t="shared" si="36"/>
         <v>0.10290882424835003</v>
       </c>
       <c r="N24" s="7">
-        <f>N5/N3</f>
+        <f t="shared" si="36"/>
         <v>0.13768243362053806</v>
       </c>
       <c r="O24" s="7">
-        <f>O5/O3</f>
+        <f t="shared" si="36"/>
         <v>8.8242365953354177E-2</v>
       </c>
       <c r="P24" s="7">
-        <f>P5/P3</f>
+        <f t="shared" si="36"/>
         <v>0.10567226890756302</v>
       </c>
       <c r="T24" s="7">
-        <f>T5/T3</f>
+        <f t="shared" ref="T24:AJ24" si="37">T5/T3</f>
         <v>0.1195589088798607</v>
       </c>
       <c r="U24" s="7">
-        <f>U5/U3</f>
+        <f t="shared" si="37"/>
         <v>0.10633855331841909</v>
       </c>
       <c r="V24" s="7">
-        <f>V5/V3</f>
+        <f t="shared" si="37"/>
         <v>9.6568800848956485E-2</v>
       </c>
       <c r="W24" s="7">
-        <f>W5/W3</f>
+        <f t="shared" si="37"/>
         <v>0.10596071501393325</v>
       </c>
       <c r="X24" s="7">
-        <f>X5/X3</f>
+        <f t="shared" si="37"/>
         <v>0.10790661173239161</v>
       </c>
       <c r="Y24" s="7">
-        <f>Y5/Y3</f>
+        <f t="shared" si="37"/>
         <v>0.11349434217193041</v>
       </c>
       <c r="Z24" s="7">
-        <f>Z5/Z3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AA24" s="7">
-        <f>AA5/AA3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AB24" s="7">
-        <f>AB5/AB3</f>
+        <f t="shared" si="37"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="AC24" s="7">
-        <f>AC5/AC3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AD24" s="7">
-        <f>AD5/AD3</f>
+        <f t="shared" si="37"/>
         <v>0.11000000000000001</v>
       </c>
       <c r="AE24" s="7">
-        <f>AE5/AE3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AF24" s="7">
-        <f>AF5/AF3</f>
+        <f t="shared" si="37"/>
         <v>0.11000000000000001</v>
       </c>
       <c r="AG24" s="7">
-        <f>AG5/AG3</f>
+        <f t="shared" si="37"/>
         <v>0.11000000000000001</v>
       </c>
       <c r="AH24" s="7">
-        <f>AH5/AH3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AI24" s="7">
-        <f>AI5/AI3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AJ24" s="7">
-        <f>AJ5/AJ3</f>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="AL24" s="1" t="s">
@@ -2985,67 +3006,67 @@
       </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7">
-        <f>U7/T7-1</f>
+        <f t="shared" ref="U25:AJ25" si="38">U7/T7-1</f>
         <v>0.34923339011925036</v>
       </c>
       <c r="V25" s="7">
-        <f>V7/U7-1</f>
+        <f t="shared" si="38"/>
         <v>-0.20959595959595956</v>
       </c>
       <c r="W25" s="7">
-        <f>W7/V7-1</f>
+        <f t="shared" si="38"/>
         <v>0.40255591054313089</v>
       </c>
       <c r="X25" s="7">
-        <f>X7/W7-1</f>
+        <f t="shared" si="38"/>
         <v>-0.17539863325740324</v>
       </c>
       <c r="Y25" s="7">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="38"/>
         <v>0.15745856353591159</v>
       </c>
       <c r="Z25" s="7">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="38"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA25" s="7">
-        <f>AA7/Z7-1</f>
+        <f t="shared" si="38"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AB25" s="7">
-        <f>AB7/AA7-1</f>
+        <f t="shared" si="38"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC25" s="7">
-        <f>AC7/AB7-1</f>
+        <f t="shared" si="38"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD25" s="7">
-        <f>AD7/AC7-1</f>
+        <f t="shared" si="38"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE25" s="7">
-        <f>AE7/AD7-1</f>
+        <f t="shared" si="38"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF25" s="7">
-        <f>AF7/AE7-1</f>
+        <f t="shared" si="38"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG25" s="7">
-        <f>AG7/AF7-1</f>
+        <f t="shared" si="38"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH25" s="7">
-        <f>AH7/AG7-1</f>
+        <f t="shared" si="38"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI25" s="7">
-        <f>AI7/AH7-1</f>
+        <f t="shared" si="38"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ25" s="7">
-        <f>AJ7/AI7-1</f>
+        <f t="shared" si="38"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL25" s="1" t="s">
@@ -3060,103 +3081,103 @@
         <v>47</v>
       </c>
       <c r="I26" s="7">
-        <f>I11/I3</f>
+        <f t="shared" ref="I26:P26" si="39">I11/I3</f>
         <v>5.0074074074074076E-2</v>
       </c>
       <c r="J26" s="7">
-        <f>J11/J3</f>
+        <f t="shared" si="39"/>
         <v>0.10911987256073277</v>
       </c>
       <c r="K26" s="7">
-        <f>K11/K3</f>
+        <f t="shared" si="39"/>
         <v>5.1310043668122272E-2</v>
       </c>
       <c r="L26" s="7">
-        <f>L11/L3</f>
+        <f t="shared" si="39"/>
         <v>5.1376996065725523E-2</v>
       </c>
       <c r="M26" s="7">
-        <f>M11/M3</f>
+        <f t="shared" si="39"/>
         <v>6.4287460278660474E-2</v>
       </c>
       <c r="N26" s="7">
-        <f>N11/N3</f>
+        <f t="shared" si="39"/>
         <v>0.11165816775101108</v>
       </c>
       <c r="O26" s="7">
-        <f>O11/O3</f>
+        <f t="shared" si="39"/>
         <v>5.0733349362827605E-2</v>
       </c>
       <c r="P26" s="7">
-        <f>P11/P3</f>
+        <f t="shared" si="39"/>
         <v>5.1050420168067226E-2</v>
       </c>
       <c r="T26" s="7">
-        <f>T11/T3</f>
+        <f t="shared" ref="T26:AJ26" si="40">T11/T3</f>
         <v>7.2040046430644225E-2</v>
       </c>
       <c r="U26" s="7">
-        <f>U11/U3</f>
+        <f t="shared" si="40"/>
         <v>3.6838180462341538E-2</v>
       </c>
       <c r="V26" s="7">
-        <f>V11/V3</f>
+        <f t="shared" si="40"/>
         <v>5.567739653342766E-2</v>
       </c>
       <c r="W26" s="7">
-        <f>W11/W3</f>
+        <f t="shared" si="40"/>
         <v>5.6344729151090872E-2</v>
       </c>
       <c r="X26" s="7">
-        <f>X11/X3</f>
+        <f t="shared" si="40"/>
         <v>6.0885488195670655E-2</v>
       </c>
       <c r="Y26" s="7">
-        <f>Y11/Y3</f>
+        <f t="shared" si="40"/>
         <v>6.6430220120475142E-2</v>
       </c>
       <c r="Z26" s="7">
-        <f>Z11/Z3</f>
+        <f t="shared" si="40"/>
         <v>6.3198102501651865E-2</v>
       </c>
       <c r="AA26" s="7">
-        <f>AA11/AA3</f>
+        <f t="shared" si="40"/>
         <v>0.10494629851255242</v>
       </c>
       <c r="AB26" s="7">
-        <f>AB11/AB3</f>
+        <f t="shared" si="40"/>
         <v>0.10499397494167929</v>
       </c>
       <c r="AC26" s="7">
-        <f>AC11/AC3</f>
+        <f t="shared" si="40"/>
         <v>0.1049458400853493</v>
       </c>
       <c r="AD26" s="7">
-        <f>AD11/AD3</f>
+        <f t="shared" si="40"/>
         <v>0.10484770105788035</v>
       </c>
       <c r="AE26" s="7">
-        <f>AE11/AE3</f>
+        <f t="shared" si="40"/>
         <v>0.10469616285370036</v>
       </c>
       <c r="AF26" s="7">
-        <f>AF11/AF3</f>
+        <f t="shared" si="40"/>
         <v>0.10454016764351506</v>
       </c>
       <c r="AG26" s="7">
-        <f>AG11/AG3</f>
+        <f t="shared" si="40"/>
         <v>0.10437958433891258</v>
       </c>
       <c r="AH26" s="7">
-        <f>AH11/AH3</f>
+        <f t="shared" si="40"/>
         <v>0.10421427799593941</v>
       </c>
       <c r="AI26" s="7">
-        <f>AI11/AI3</f>
+        <f t="shared" si="40"/>
         <v>0.10404410970170234</v>
       </c>
       <c r="AJ26" s="7">
-        <f>AJ11/AJ3</f>
+        <f t="shared" si="40"/>
         <v>0.10386893645763476</v>
       </c>
       <c r="AL26" s="1" t="s">
@@ -3172,23 +3193,23 @@
         <v>40</v>
       </c>
       <c r="T27" s="7">
-        <f t="shared" ref="T27:X27" si="33">T17/T16</f>
+        <f t="shared" ref="T27:X27" si="41">T17/T16</f>
         <v>0.16915995397008055</v>
       </c>
       <c r="U27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>4.7430830039525688E-2</v>
       </c>
       <c r="V27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0.22045152722443559</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>5.188199389623601E-2</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0.15655339805825244</v>
       </c>
       <c r="Y27" s="7">
@@ -3196,47 +3217,47 @@
         <v>0.19986168741355465</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" ref="Z27:AJ27" si="34">Z17/Z16</f>
+        <f t="shared" ref="Z27:AJ27" si="42">Z17/Z16</f>
         <v>0.18</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AE27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AF27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AH27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AI27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AJ27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0.18</v>
       </c>
       <c r="AL27" s="1" t="s">
@@ -3252,71 +3273,71 @@
         <v>48</v>
       </c>
       <c r="T28" s="7">
-        <f>T19/T3</f>
+        <f t="shared" ref="T28:AJ28" si="43">T19/T3</f>
         <v>5.9706906558328499E-2</v>
       </c>
       <c r="U28" s="7">
-        <f>U19/U3</f>
+        <f t="shared" si="43"/>
         <v>1.7822520507084265E-2</v>
       </c>
       <c r="V28" s="7">
-        <f>V19/V3</f>
+        <f t="shared" si="43"/>
         <v>4.145737530951539E-2</v>
       </c>
       <c r="W28" s="7">
-        <f>W19/W3</f>
+        <f t="shared" si="43"/>
         <v>6.3005505335417655E-2</v>
       </c>
       <c r="X28" s="7">
-        <f>X19/X3</f>
+        <f t="shared" si="43"/>
         <v>4.3031848799947682E-2</v>
       </c>
       <c r="Y28" s="7">
-        <f>Y19/Y3</f>
+        <f t="shared" si="43"/>
         <v>6.0350166075550299E-2</v>
       </c>
       <c r="Z28" s="7">
-        <f>Z19/Z3</f>
+        <f t="shared" si="43"/>
         <v>5.023712062625741E-2</v>
       </c>
       <c r="AA28" s="7">
-        <f>AA19/AA3</f>
+        <f t="shared" si="43"/>
         <v>8.1341828088976942E-2</v>
       </c>
       <c r="AB28" s="7">
-        <f>AB19/AB3</f>
+        <f t="shared" si="43"/>
         <v>8.1278260723857479E-2</v>
       </c>
       <c r="AC28" s="7">
-        <f>AC19/AC3</f>
+        <f t="shared" si="43"/>
         <v>8.119345228319462E-2</v>
       </c>
       <c r="AD28" s="7">
-        <f>AD19/AD3</f>
+        <f t="shared" si="43"/>
         <v>8.1095730806581431E-2</v>
       </c>
       <c r="AE28" s="7">
-        <f>AE19/AE3</f>
+        <f t="shared" si="43"/>
         <v>8.0982077153446422E-2</v>
       </c>
       <c r="AF28" s="7">
-        <f>AF19/AF3</f>
+        <f t="shared" si="43"/>
         <v>8.0865080745807477E-2</v>
       </c>
       <c r="AG28" s="7">
-        <f>AG19/AG3</f>
+        <f t="shared" si="43"/>
         <v>8.0744643267355601E-2</v>
       </c>
       <c r="AH28" s="7">
-        <f>AH19/AH3</f>
+        <f t="shared" si="43"/>
         <v>8.0620663510125729E-2</v>
       </c>
       <c r="AI28" s="7">
-        <f>AI19/AI3</f>
+        <f t="shared" si="43"/>
         <v>8.0493037289447913E-2</v>
       </c>
       <c r="AJ28" s="7">
-        <f>AJ19/AJ3</f>
+        <f t="shared" si="43"/>
         <v>8.0361657356397248E-2</v>
       </c>
       <c r="AL28" s="1" t="s">
@@ -3342,16 +3363,22 @@
       </c>
       <c r="AM30" s="8">
         <f>Main!D3</f>
-        <v>47.27</v>
-      </c>
-    </row>
-    <row r="31" spans="2:142" x14ac:dyDescent="0.3">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:142" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="O31" s="12">
+        <v>32696</v>
+      </c>
       <c r="AL31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="AM31" s="9">
         <f>AM29/AM30-1</f>
-        <v>-0.10935664388414268</v>
+        <v>-0.24550696337640532</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">
@@ -3360,6 +3387,24 @@
       </c>
       <c r="AM32" s="2" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O33" s="13">
+        <f>Main!D9/Model!O31</f>
+        <v>0.99186811842427192</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O34" s="7">
+        <f>O31/Main!D9-1</f>
+        <v>8.1985512233690994E-3</v>
       </c>
     </row>
   </sheetData>
